--- a/resources/excel/templates/contoh_discord_export_ziarah.xlsx
+++ b/resources/excel/templates/contoh_discord_export_ziarah.xlsx
@@ -20,24 +20,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
-  <si>
-    <t xml:space="preserve">DATA BOOKING ZIARAH</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+  <si>
+    <t xml:space="preserve">DATA BOOKING </t>
   </si>
   <si>
     <t xml:space="preserve">TANGGAL: 12 Mei 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Ziarah</t>
+    <t xml:space="preserve">Data </t>
   </si>
   <si>
     <t xml:space="preserve">Fasilitas</t>
   </si>
   <si>
+    <t xml:space="preserve">Nomor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kode Booking</t>
   </si>
   <si>
-    <t xml:space="preserve">Jam Ziarah</t>
+    <t xml:space="preserve">Jenis Kegiatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jam </t>
   </si>
   <si>
     <t xml:space="preserve">Lokasi</t>
@@ -187,27 +193,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -401,271 +407,301 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="17.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="15.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="N4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="5"/>
       <c r="I14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="I14:J14"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
